--- a/data/000800_一汽解放_财务数据.xlsx
+++ b/data/000800_一汽解放_财务数据.xlsx
@@ -10682,7 +10682,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>归属于少数股东的综合收益总额</t>
+          <t>minority_common_profit_total</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
@@ -17427,7 +17427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -17457,8 +17457,6 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17505,22 +17503,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>财务费用率(%)</t>
+          <t>资产负债率(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>资产负债率(%)</t>
+          <t>流动比率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>流动比率</t>
+          <t>速动比率</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>速动比率</t>
+          <t>产权比率(%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -17530,75 +17528,65 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>应收账款周转天数(天)</t>
+          <t>存货周转率(次)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>存货周转率(次)</t>
+          <t>总资产周转率(次)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>存货周转天数(天)</t>
+          <t>流动资产周转率(次)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>总资产周转率(次)</t>
+          <t>固定资产周转率(次)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>流动资产周转率(次)</t>
+          <t>营收同比(%)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>固定资产周转率(次)</t>
+          <t>净利润同比(%)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>营收同比(%)</t>
+          <t>总资产增长率(%)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>净利润同比(%)</t>
+          <t>经营现金流/净利润</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>总资产增长率(%)</t>
+          <t>自由现金流(元)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>经营现金流/净利润</t>
+          <t>现金收入比</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>自由现金流(元)</t>
+          <t>现金流组合</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>现金收入比</t>
+          <t>Altman Z-score</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>现金流组合</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Altman Z-score</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Z-score判定</t>
         </is>
@@ -17632,58 +17620,52 @@
         <v>7.890111656324068</v>
       </c>
       <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="6" t="n">
-        <v>0.488425409200251</v>
-      </c>
-      <c r="K2" s="3" t="n">
+      <c r="J2" s="3" t="n">
         <v>59.71442070449893</v>
       </c>
+      <c r="K2" s="6" t="n">
+        <v>0.9757709251101322</v>
+      </c>
       <c r="L2" s="6" t="n">
-        <v>0.9757709251101322</v>
-      </c>
-      <c r="M2" s="6" t="n">
         <v>0.718245227606461</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>148.2277821214491</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>3.446539949019975</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>104.452582974518</v>
+        <v>8.369600325</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>8.369600325</v>
+        <v>1.159400913083102</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>43.01280658822857</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>1.159400913083102</v>
-      </c>
-      <c r="S2" s="3" t="n">
         <v>2.07725996927389</v>
       </c>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
+      <c r="V2" s="6" t="n">
+        <v>-0.5664495186937767</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>-291000000</v>
+      </c>
       <c r="X2" s="6" t="n">
-        <v>-0.5664495186937767</v>
-      </c>
-      <c r="Y2" s="3" t="n">
-        <v>-291000000</v>
-      </c>
-      <c r="Z2" s="6" t="n">
         <v>0.8292345525538055</v>
       </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>1.656072043769619</v>
+      </c>
       <c r="AA2" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>1.656072043769619</v>
-      </c>
-      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -17719,64 +17701,58 @@
       <c r="I3" s="3" t="n">
         <v>1.686541774355482</v>
       </c>
-      <c r="J3" s="6" t="n">
-        <v>0.1093301540786038</v>
+      <c r="J3" s="3" t="n">
+        <v>57.16062736614386</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>57.16062736614386</v>
-      </c>
-      <c r="L3" s="3" t="n">
         <v>1.068174962292609</v>
       </c>
-      <c r="M3" s="6" t="n">
+      <c r="L3" s="6" t="n">
         <v>0.8507792860734037</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>133.4301224592855</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>4.107931804169739</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>87.63533991352621</v>
+        <v>10.99370259767311</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>10.99370259767311</v>
+        <v>1.454447950377474</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>32.74601953269106</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>1.454447950377474</v>
-      </c>
+        <v>2.568737784484592</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="3" t="n">
-        <v>2.568737784484592</v>
-      </c>
-      <c r="T3" s="4" t="inlineStr"/>
+        <v>23.60756971912424</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>124.4661581533348</v>
+      </c>
       <c r="U3" s="3" t="n">
-        <v>23.60756971912424</v>
+        <v>-2.934537246049661</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>124.4661581533348</v>
+        <v>9.313937129506293</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>-2.934537246049661</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>9.313937129506293</v>
-      </c>
-      <c r="Y3" s="3" t="n">
         <v>1909000000</v>
       </c>
-      <c r="Z3" s="6" t="n">
+      <c r="X3" s="6" t="n">
         <v>0.8576422697879889</v>
       </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>2.33033828580738</v>
+      </c>
       <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>2.33033828580738</v>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -17812,64 +17788,58 @@
       <c r="I4" s="3" t="n">
         <v>1.813503008716048</v>
       </c>
-      <c r="J4" s="6" t="n">
-        <v>-0.08526464081091222</v>
+      <c r="J4" s="3" t="n">
+        <v>56.33455013957484</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>56.33455013957484</v>
-      </c>
-      <c r="L4" s="3" t="n">
         <v>1.030670993405213</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="L4" s="6" t="n">
         <v>0.8015283157123416</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>129.0140152446521</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>3.734374321192392</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>96.40169116336774</v>
+        <v>11.81700898822799</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>11.81700898822799</v>
+        <v>1.375313782280834</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>30.46456174812332</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>1.375313782280834</v>
-      </c>
+        <v>2.493961452474474</v>
+      </c>
+      <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="3" t="n">
-        <v>2.493961452474474</v>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="3" t="n">
         <v>-6.501320061238768</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>12.29783204802737</v>
       </c>
-      <c r="W4" s="6" t="n">
+      <c r="U4" s="6" t="n">
         <v>0.7463493780421849</v>
       </c>
+      <c r="V4" s="6" t="n">
+        <v>0.3092278620389903</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>-415807200</v>
+      </c>
       <c r="X4" s="6" t="n">
-        <v>0.3092278620389903</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>-415807200</v>
-      </c>
-      <c r="Z4" s="6" t="n">
         <v>0.8132203135324816</v>
       </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>2.20879963155624</v>
+      </c>
       <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>2.20879963155624</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -17905,64 +17875,58 @@
       <c r="I5" s="3" t="n">
         <v>2.43679490919003</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>-0.6644001108377295</v>
+      <c r="J5" s="3" t="n">
+        <v>65.48037102516287</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>65.48037102516287</v>
-      </c>
-      <c r="L5" s="3" t="n">
         <v>1.212300784726155</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="L5" s="6" t="n">
         <v>0.8140320362430224</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>189.6902515171712</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>24.68345889820522</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>14.58466584787176</v>
+        <v>9.560896761072163</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>9.560896761072163</v>
+        <v>2.103496028031024</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>37.65337174916105</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>2.103496028031024</v>
-      </c>
+        <v>3.05063741093642</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="3" t="n">
-        <v>3.05063741093642</v>
-      </c>
-      <c r="T5" s="4" t="inlineStr"/>
+        <v>317.0410050568047</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>616.0058557784283</v>
+      </c>
       <c r="U5" s="3" t="n">
-        <v>317.0410050568047</v>
+        <v>343.3218810392957</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>616.0058557784283</v>
+        <v>8.432490265620519</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>343.3218810392957</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>8.432490265620519</v>
-      </c>
-      <c r="Y5" s="3" t="n">
         <v>14493000000</v>
       </c>
-      <c r="Z5" s="6" t="n">
+      <c r="X5" s="6" t="n">
         <v>0.9163961250423155</v>
       </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>1.963812541791897</v>
+      </c>
       <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>1.963812541791897</v>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -17999,63 +17963,57 @@
         <v>2.495115093759301</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-1.089153216912099</v>
+        <v>61.76562159469473</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>61.76562159469473</v>
-      </c>
-      <c r="L6" s="3" t="n">
         <v>1.329864396089562</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="L6" s="6" t="n">
         <v>0.7575470886729165</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>161.5447253776312</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>75.81266091891963</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>4.748547216737505</v>
+        <v>5.592235541556929</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>5.592235541556929</v>
+        <v>1.548577646750034</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>64.37497085463835</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>1.548577646750034</v>
-      </c>
+        <v>2.138309477238733</v>
+      </c>
+      <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="3" t="n">
-        <v>2.138309477238733</v>
-      </c>
-      <c r="T6" s="4" t="inlineStr"/>
+        <v>6.795532280026033</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>33.864710955097</v>
+      </c>
       <c r="U6" s="3" t="n">
-        <v>6.795532280026033</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>33.864710955097</v>
+        <v>-22.21307306677</v>
+      </c>
+      <c r="V6" s="6" t="n">
+        <v>-0.295384463990045</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-22.21307306677</v>
+        <v>-2686000000</v>
       </c>
       <c r="X6" s="6" t="n">
-        <v>-0.295384463990045</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>-2686000000</v>
-      </c>
-      <c r="Z6" s="6" t="n">
         <v>0.8519007358099804</v>
       </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>2.744576828204906</v>
+      </c>
       <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>2.744576828204906</v>
-      </c>
-      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18092,63 +18050,57 @@
         <v>3.371042817394826</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-1.236070484211115</v>
+        <v>62.38568930424562</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>62.38568930424562</v>
+        <v>1.294585904682881</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.294585904682881</v>
+        <v>1.054270601047555</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.054270601047555</v>
+        <v>165.8562609557198</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>80.48186036638143</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>4.473057635113736</v>
+        <v>6.533637815422668</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>6.533637815422668</v>
+        <v>1.473855148645563</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>55.0994729383712</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>1.473855148645563</v>
-      </c>
+        <v>2.050610350926137</v>
+      </c>
+      <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="3" t="n">
-        <v>2.050610350926137</v>
-      </c>
-      <c r="T7" s="4" t="inlineStr"/>
+        <v>-13.13309278502806</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>47.68673179959303</v>
+      </c>
       <c r="U7" s="3" t="n">
-        <v>-13.13309278502806</v>
+        <v>8.60549830318503</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>47.68673179959303</v>
+        <v>3.898350306379011</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>8.60549830318503</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>3.898350306379011</v>
-      </c>
-      <c r="Y7" s="3" t="n">
         <v>12711000000</v>
       </c>
-      <c r="Z7" s="6" t="n">
+      <c r="X7" s="6" t="n">
         <v>0.8694371602725599</v>
       </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>+/+/−</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>2.391630185396559</v>
+      </c>
       <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>+/+/−</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>2.391630185396559</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18185,63 +18137,57 @@
         <v>7.554195459428294</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-2.746028796617673</v>
+        <v>58.23428943707852</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>58.23428943707852</v>
+        <v>1.256253813300793</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>1.256253813300793</v>
+        <v>1.027168646592255</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.027168646592255</v>
+        <v>139.4367384796998</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>32.66446278984235</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>11.02115171206639</v>
-      </c>
-      <c r="P8" s="3" t="n">
         <v>5.18807040009584</v>
       </c>
-      <c r="Q8" s="3" t="n">
-        <v>69.38996047419667</v>
-      </c>
-      <c r="R8" s="6" t="n">
+      <c r="P8" s="6" t="n">
         <v>0.6057530019023538</v>
       </c>
-      <c r="S8" s="6" t="n">
+      <c r="Q8" s="6" t="n">
         <v>0.9026668334835747</v>
       </c>
-      <c r="T8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="3" t="n">
+        <v>-61.18352939400567</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-90.57800517875557</v>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>-61.18352939400567</v>
+        <v>-18.59501763036437</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>-90.57800517875557</v>
+        <v>-13.97491430805437</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>-18.59501763036437</v>
+        <v>-7964000000</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>-13.97491430805437</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>-7964000000</v>
+        <v>1.069870358641866</v>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>−/−/−</t>
+        </is>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>1.069870358641866</v>
+        <v>1.477039421993966</v>
       </c>
       <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>−/−/−</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="n">
-        <v>1.477039421993966</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -18278,63 +18224,57 @@
         <v>4.636260449232397</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-1.450558989963119</v>
+        <v>63.21123285256881</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>63.21123285256881</v>
-      </c>
-      <c r="L9" s="3" t="n">
         <v>1.164809754046668</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="L9" s="6" t="n">
         <v>0.9005413075467732</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>171.8289615522817</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>37.3763165430796</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>9.631767742149425</v>
+        <v>7.880082475266423</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>7.880082475266423</v>
+        <v>1.030191477680635</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>45.68480103221616</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>1.030191477680635</v>
-      </c>
+        <v>1.62167729565088</v>
+      </c>
+      <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="3" t="n">
-        <v>1.62167729565088</v>
-      </c>
-      <c r="T9" s="4" t="inlineStr"/>
+        <v>67.81035476906565</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>125.4219520990494</v>
+      </c>
       <c r="U9" s="3" t="n">
-        <v>67.81035476906565</v>
+        <v>19.88449280721217</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>125.4219520990494</v>
+        <v>4.937826285951593</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>19.88449280721217</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>4.937826285951593</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>1838000000</v>
       </c>
-      <c r="Z9" s="6" t="n">
+      <c r="X9" s="6" t="n">
         <v>0.960331830227575</v>
       </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>1.622072456890327</v>
+      </c>
       <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="n">
-        <v>1.622072456890327</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -18371,63 +18311,57 @@
         <v>4.113076375045674</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-1.375821861545406</v>
+        <v>63.44417105389765</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>63.44417105389765</v>
-      </c>
-      <c r="L10" s="3" t="n">
         <v>1.225262286701882</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="L10" s="6" t="n">
         <v>0.9789927216961612</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>173.5476593344614</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>12.38763084341933</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>29.06124702539409</v>
-      </c>
-      <c r="P10" s="3" t="n">
         <v>5.927032674948944</v>
       </c>
+      <c r="P10" s="6" t="n">
+        <v>0.8319111905212483</v>
+      </c>
       <c r="Q10" s="3" t="n">
-        <v>60.7386562118288</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>0.8319111905212483</v>
-      </c>
+        <v>1.237676943653381</v>
+      </c>
+      <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="3" t="n">
-        <v>1.237676943653381</v>
-      </c>
-      <c r="T10" s="4" t="inlineStr"/>
+        <v>-8.928980315007914</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>-20.40668886681766</v>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>-8.928980315007914</v>
+        <v>6.848691360925888</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>-20.40668886681766</v>
+        <v>-8.873435428927586</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>6.848691360925888</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>-8.873435428927586</v>
-      </c>
-      <c r="Y10" s="3" t="n">
         <v>-7364000000</v>
       </c>
-      <c r="Z10" s="6" t="n">
+      <c r="X10" s="6" t="n">
         <v>0.9357965989592022</v>
       </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>−/+/+</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>1.496730872474325</v>
+      </c>
       <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>−/+/+</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="n">
-        <v>1.496730872474325</v>
-      </c>
-      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -18463,64 +18397,58 @@
       <c r="I11" s="3" t="n">
         <v>3.642709119389251</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>-0.9618623636776304</v>
+      <c r="J11" s="3" t="n">
+        <v>63.00995779659614</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>63.00995779659614</v>
-      </c>
-      <c r="L11" s="3" t="n">
         <v>1.238370127047003</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="L11" s="6" t="n">
         <v>0.9143519636732526</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>170.3493791714829</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>9.694973091885538</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>37.13264560799157</v>
-      </c>
-      <c r="P11" s="3" t="n">
         <v>5.352648838877274</v>
       </c>
+      <c r="P11" s="6" t="n">
+        <v>0.8630064512621253</v>
+      </c>
       <c r="Q11" s="3" t="n">
-        <v>67.25642029517306</v>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>0.8630064512621253</v>
-      </c>
+        <v>1.233746059072102</v>
+      </c>
+      <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="3" t="n">
-        <v>1.233746059072102</v>
-      </c>
-      <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="3" t="n">
         <v>6.993542871023288</v>
       </c>
+      <c r="T11" s="3" t="n">
+        <v>19.60984793600244</v>
+      </c>
+      <c r="U11" s="6" t="n">
+        <v>-0.3340252099685219</v>
+      </c>
       <c r="V11" s="3" t="n">
-        <v>19.60984793600244</v>
-      </c>
-      <c r="W11" s="6" t="n">
-        <v>-0.3340252099685219</v>
-      </c>
-      <c r="X11" s="3" t="n">
         <v>3.404969915246028</v>
       </c>
-      <c r="Y11" s="3" t="n">
+      <c r="W11" s="3" t="n">
         <v>1643000000</v>
       </c>
-      <c r="Z11" s="6" t="n">
+      <c r="X11" s="6" t="n">
         <v>0.9727974566709935</v>
       </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>1.586221384119981</v>
+      </c>
       <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="n">
-        <v>1.586221384119981</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
